--- a/files/九龙-何文田-朗贤峰第IIA期.xlsx
+++ b/files/九龙-何文田-朗贤峰第IIA期.xlsx
@@ -23925,7 +23925,7 @@
         </is>
       </c>
       <c r="E351" s="4" t="n">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F351" s="3" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>12297000</v>
       </c>
       <c r="I351" s="5" t="n">
-        <v>20461</v>
+        <v>20427</v>
       </c>
       <c r="J351" s="3" t="inlineStr">
         <is>
@@ -23952,7 +23952,7 @@
         <v>12297000</v>
       </c>
       <c r="L351" s="5" t="n">
-        <v>20461</v>
+        <v>20427</v>
       </c>
       <c r="M351" s="3" t="inlineStr">
         <is>
@@ -32066,9 +32066,9 @@
       </c>
       <c r="H19" s="23" t="inlineStr">
         <is>
-          <t>G | 601呎 (2房)
+          <t>G | 602呎 (2房)
 $1230万
-$20,461/呎
+$20,427/呎
 (24年-10月-03日)</t>
         </is>
       </c>

--- a/files/九龙-何文田-朗贤峰第IIA期.xlsx
+++ b/files/九龙-何文田-朗贤峰第IIA期.xlsx
@@ -11645,7 +11645,7 @@
         </is>
       </c>
       <c r="E167" s="4" t="n">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>25297000</v>
       </c>
       <c r="I167" s="5" t="n">
-        <v>26106</v>
+        <v>26133</v>
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>25297000</v>
       </c>
       <c r="L167" s="5" t="n">
-        <v>26106</v>
+        <v>26133</v>
       </c>
       <c r="M167" s="3" t="inlineStr">
         <is>
@@ -20643,7 +20643,7 @@
         </is>
       </c>
       <c r="E300" s="4" t="n">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="F300" s="3" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>22501000</v>
       </c>
       <c r="I300" s="5" t="n">
-        <v>22705</v>
+        <v>22682</v>
       </c>
       <c r="J300" s="3" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         <v>22501000</v>
       </c>
       <c r="L300" s="5" t="n">
-        <v>22705</v>
+        <v>22682</v>
       </c>
       <c r="M300" s="3" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         </is>
       </c>
       <c r="E351" s="4" t="n">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F351" s="3" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>12297000</v>
       </c>
       <c r="I351" s="5" t="n">
-        <v>20427</v>
+        <v>20461</v>
       </c>
       <c r="J351" s="3" t="inlineStr">
         <is>
@@ -23952,7 +23952,7 @@
         <v>12297000</v>
       </c>
       <c r="L351" s="5" t="n">
-        <v>20427</v>
+        <v>20461</v>
       </c>
       <c r="M351" s="3" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         </is>
       </c>
       <c r="E357" s="4" t="n">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="F357" s="3" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>21944000</v>
       </c>
       <c r="I357" s="5" t="n">
-        <v>22143</v>
+        <v>22121</v>
       </c>
       <c r="J357" s="3" t="inlineStr">
         <is>
@@ -24324,7 +24324,7 @@
         <v>21944000</v>
       </c>
       <c r="L357" s="5" t="n">
-        <v>22143</v>
+        <v>22121</v>
       </c>
       <c r="M357" s="3" t="inlineStr">
         <is>
@@ -30201,9 +30201,9 @@
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t>E | 969呎 (3房)
+          <t>E | 968呎 (3房)
 $2530万
-$26,106/呎
+$26,133/呎
 (24年-05月-23日)</t>
         </is>
       </c>
@@ -31500,9 +31500,9 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>A | 991呎 (3房)
+          <t>A | 992呎 (3房)
 $2250万
-$22,705/呎
+$22,682/呎
 (24年-05月-29日)</t>
         </is>
       </c>
@@ -32018,9 +32018,9 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>A | 991呎 (3房)
+          <t>A | 992呎 (3房)
 $2194万
-$22,143/呎
+$22,121/呎
 (24年-05月-17日)</t>
         </is>
       </c>
@@ -32066,9 +32066,9 @@
       </c>
       <c r="H19" s="23" t="inlineStr">
         <is>
-          <t>G | 602呎 (2房)
+          <t>G | 601呎 (2房)
 $1230万
-$20,427/呎
+$20,461/呎
 (24年-10月-03日)</t>
         </is>
       </c>
